--- a/Project_Organizational_Structure_Chart/Project_Organizational_Structure_Chart.xlsx
+++ b/Project_Organizational_Structure_Chart/Project_Organizational_Structure_Chart.xlsx
@@ -45,43 +45,43 @@
     <t>CONTRACTOR</t>
   </si>
   <si>
-    <t xml:space="preserve">TTT Project </t>
-  </si>
-  <si>
-    <t>PROPOSAL OF SITE ORGNIZATION CHART FOR TBM ASSEMBLY. TUNNEL EXCAVATION, TBM DISASSEMBLY</t>
-  </si>
-  <si>
-    <t>SELI OVERSEAS (ROME)</t>
+    <t xml:space="preserve">Coastal Tunnel Package </t>
+  </si>
+  <si>
+    <t>PROPOSAL OF SITE ORGANIZATION CHART FOR TBM ASSEMBLY. TUNNEL EXCAVATION, TBM DISASSEMBLY</t>
+  </si>
+  <si>
+    <t>APEX TUNNEL SERVICES</t>
   </si>
   <si>
     <t>Head Office Support</t>
   </si>
   <si>
-    <t>SELI SITE PERSONNEL</t>
+    <t>SPECIALIST SITE PERSONNEL</t>
   </si>
   <si>
     <t>TECHNICAL SERVICE</t>
   </si>
   <si>
-    <t>SELI PERSONNEL @ SELI COSST</t>
-  </si>
-  <si>
-    <t>AC PERSONNEL</t>
-  </si>
-  <si>
-    <t>HK PERSONNEL</t>
+    <t>SPECIALIST PERSONNEL @ HEAD OFFICE</t>
+  </si>
+  <si>
+    <t>JV PERSONNEL</t>
+  </si>
+  <si>
+    <t>TBM SUPPLIER PERSONNEL</t>
   </si>
   <si>
     <t>PRE-EXECUTION STAGE</t>
   </si>
   <si>
-    <t>AC PERSONNEL WILL BE BRING</t>
-  </si>
-  <si>
-    <t>VINCI PERSONNEL WILL BE BRING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Presonnel in Ac's office in Cairo </t>
+    <t>JV PERSONNEL TO BE MOBILISED</t>
+  </si>
+  <si>
+    <t>PARTNER PERSONNEL TO BE MOBILISED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personnel in JV head office </t>
   </si>
   <si>
     <t>TOTAL FOR TUNNELING WORKS</t>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Plant Manager </t>
   </si>
   <si>
-    <t>E.Mohamed Saleh</t>
+    <t>Eng. Daniel Rafiq</t>
   </si>
   <si>
     <t>Shift Engnieers</t>
@@ -150,10 +150,10 @@
     <t>TBM Elec. Manager</t>
   </si>
   <si>
-    <t>E.Ahmed Khaled</t>
-  </si>
-  <si>
-    <t>E.Mohamed Sayed</t>
+    <t>Eng. Oscar Faris</t>
+  </si>
+  <si>
+    <t>Eng. Emil Silva</t>
   </si>
   <si>
     <t>Underground - Tunnel</t>
@@ -195,13 +195,13 @@
     <t>Elec. Shift Engineer</t>
   </si>
   <si>
-    <t>E.Magdy Abousoud</t>
-  </si>
-  <si>
-    <t>E.Mahmoud shaaban</t>
-  </si>
-  <si>
-    <t>E.Mohamed Ali</t>
+    <t>Eng. Tomas Menon</t>
+  </si>
+  <si>
+    <t>Eng. Emil Nasser</t>
+  </si>
+  <si>
+    <t>Eng. Carlos Ortega</t>
   </si>
   <si>
     <t>G.Foreman</t>
@@ -210,16 +210,16 @@
     <t>PLC. Shift Engineer</t>
   </si>
   <si>
-    <t>Yasser Salama</t>
-  </si>
-  <si>
-    <t>Abdelsalam</t>
-  </si>
-  <si>
-    <t>Emad hamdy</t>
-  </si>
-  <si>
-    <t>E.khaled Bahnas</t>
+    <t>Bruno Darwish</t>
+  </si>
+  <si>
+    <t>Cyril Haddad</t>
+  </si>
+  <si>
+    <t>Tomas Baig</t>
+  </si>
+  <si>
+    <t>Eng. Daniel Faris</t>
   </si>
   <si>
     <t>Mechanic</t>
@@ -228,22 +228,22 @@
     <t>Elect. Supervisor</t>
   </si>
   <si>
-    <t>Mohamed abdelazim</t>
-  </si>
-  <si>
-    <t>Ahmed Zayan</t>
-  </si>
-  <si>
-    <t>Ahmed Nasser</t>
-  </si>
-  <si>
-    <t>Abdelalim</t>
-  </si>
-  <si>
-    <t>Ahmed abdelkader</t>
-  </si>
-  <si>
-    <t>Ahmed Azab</t>
+    <t>Faris Mendes</t>
+  </si>
+  <si>
+    <t>Umar Novak</t>
+  </si>
+  <si>
+    <t>Cyril Petrov</t>
+  </si>
+  <si>
+    <t>Cyril Karam</t>
+  </si>
+  <si>
+    <t>Bruno Haddad</t>
+  </si>
+  <si>
+    <t>Bilal Mendes</t>
   </si>
   <si>
     <t>TBM Foreman/Shift leader</t>
@@ -255,19 +255,19 @@
     <t>Helper</t>
   </si>
   <si>
-    <t>Mostafa neenaa</t>
+    <t>Gavin Costa</t>
   </si>
   <si>
     <t>Welder</t>
   </si>
   <si>
-    <t>Tamer Tolb</t>
-  </si>
-  <si>
-    <t>Tamer Abdelhamid</t>
-  </si>
-  <si>
-    <t>Emad Elbalat</t>
+    <t>Victor Nasser</t>
+  </si>
+  <si>
+    <t>Bruno Quinn</t>
+  </si>
+  <si>
+    <t>Marco Darwish</t>
   </si>
   <si>
     <t>TBM Operator</t>
@@ -282,10 +282,10 @@
     <t>STP&amp;surface Elec. Manager</t>
   </si>
   <si>
-    <t>E.Ahmed Elkei</t>
-  </si>
-  <si>
-    <t>E.Tarek Fawzi</t>
+    <t>Eng. Felix Novak</t>
+  </si>
+  <si>
+    <t>Eng. Karim Petrov</t>
   </si>
   <si>
     <t>TBM Erector</t>
@@ -294,10 +294,10 @@
     <t>Bottom Rigger</t>
   </si>
   <si>
-    <t>Amer Elsayed sayed</t>
-  </si>
-  <si>
-    <t>Walid ahmed Moussa</t>
+    <t>Bruno Karam</t>
+  </si>
+  <si>
+    <t>Rami Varga</t>
   </si>
   <si>
     <t>STP &amp; Surface Mechanical  (assembly, disassembly and maintenance)</t>
@@ -318,13 +318,13 @@
     <t xml:space="preserve">STP &amp;Surface Electric </t>
   </si>
   <si>
-    <t>Ibrahim Abdallah</t>
-  </si>
-  <si>
-    <t>Abdelnabi Abdelnabi</t>
-  </si>
-  <si>
-    <t>Mahmoud saiid</t>
+    <t>Zane Costa</t>
+  </si>
+  <si>
+    <t>Bruno Petrov</t>
+  </si>
+  <si>
+    <t>Oscar Novak</t>
   </si>
   <si>
     <t>TBM Assistant</t>
@@ -333,31 +333,31 @@
     <t>Grout Plant Operator</t>
   </si>
   <si>
-    <t>Gamal Abdelfatah</t>
-  </si>
-  <si>
-    <t>Abdelnabi Mostafa</t>
-  </si>
-  <si>
-    <t>Mohamed Ashri</t>
-  </si>
-  <si>
-    <t>Mahmoud Mostafa</t>
-  </si>
-  <si>
-    <t>Ahmed farrag</t>
-  </si>
-  <si>
-    <t>Reda Abdelmenoim</t>
-  </si>
-  <si>
-    <t>E.Peter</t>
-  </si>
-  <si>
-    <t>E.Emam Reda</t>
-  </si>
-  <si>
-    <t>E.Mohamed Kotb</t>
+    <t>Cyril Nasser</t>
+  </si>
+  <si>
+    <t>Hadi Varga</t>
+  </si>
+  <si>
+    <t>Wael Rafiq</t>
+  </si>
+  <si>
+    <t>Emil Menon</t>
+  </si>
+  <si>
+    <t>Samir Darwish</t>
+  </si>
+  <si>
+    <t>Leo Nasser</t>
+  </si>
+  <si>
+    <t>Eng. Pavel Arslan</t>
+  </si>
+  <si>
+    <t>Eng. Adam Nasser</t>
+  </si>
+  <si>
+    <t>Eng. Nabil Novak</t>
   </si>
   <si>
     <t>Segment Crane Operator</t>
@@ -369,28 +369,28 @@
     <t>Electrical supervisor</t>
   </si>
   <si>
-    <t>Abd Elaleem</t>
-  </si>
-  <si>
-    <t>Ahmed Abdelqader</t>
-  </si>
-  <si>
-    <t>Atris</t>
-  </si>
-  <si>
-    <t>Ahmed Henawy</t>
-  </si>
-  <si>
-    <t>Ali Salah</t>
-  </si>
-  <si>
-    <t>Hossam Hassan</t>
-  </si>
-  <si>
-    <t>Mohamed Fawzi</t>
-  </si>
-  <si>
-    <t>Mohamed Hassan</t>
+    <t>Daniel Morris</t>
+  </si>
+  <si>
+    <t>Elias Morris</t>
+  </si>
+  <si>
+    <t>Marco Quinn</t>
+  </si>
+  <si>
+    <t>Tomas Silva</t>
+  </si>
+  <si>
+    <t>Oscar Petrov</t>
+  </si>
+  <si>
+    <t>Samir Morris</t>
+  </si>
+  <si>
+    <t>Bilal Nasser</t>
+  </si>
+  <si>
+    <t>Adam Mendes</t>
   </si>
   <si>
     <t>Pipe Extension</t>
@@ -399,19 +399,19 @@
     <t>Grout Plant Labor</t>
   </si>
   <si>
-    <t>Kamal Nasser</t>
-  </si>
-  <si>
-    <t>Mohamed Mhmoud sayed</t>
-  </si>
-  <si>
-    <t>Mahmoud Abdelaziz</t>
+    <t>Elias Rafiq</t>
+  </si>
+  <si>
+    <t>Leo Costa</t>
+  </si>
+  <si>
+    <t>Ivan Novak</t>
   </si>
   <si>
     <t>Forklift Operator</t>
   </si>
   <si>
-    <t>Mehanna</t>
+    <t>Faris Baig</t>
   </si>
   <si>
     <t xml:space="preserve"> Mechanical Workshop (Cutter head discs, hydraulic container and maintainance)</t>
@@ -432,7 +432,7 @@
     <t>STP Manager</t>
   </si>
   <si>
-    <t>E. Rda Sobhy</t>
+    <t>Eng. Rami Menon</t>
   </si>
   <si>
     <t>WTP</t>
@@ -444,7 +444,7 @@
     <t>Supervisor</t>
   </si>
   <si>
-    <t>Mohamed Saber</t>
+    <t>Zane Varga</t>
   </si>
   <si>
     <t>Grout Operator</t>
@@ -456,16 +456,16 @@
     <t>STP Operator</t>
   </si>
   <si>
-    <t>Ayman Fathy</t>
-  </si>
-  <si>
-    <t>Mohamed Elsayed</t>
-  </si>
-  <si>
-    <t>E. Alaa Emad</t>
-  </si>
-  <si>
-    <t>E. Ahmed Diab</t>
+    <t>Carlos Haddad</t>
+  </si>
+  <si>
+    <t>Rami Ortega</t>
+  </si>
+  <si>
+    <t>Eng. Adam Quinn</t>
+  </si>
+  <si>
+    <t>Eng. Leo Petrov</t>
   </si>
   <si>
     <t>Electrician</t>
@@ -486,16 +486,16 @@
     <t>STP Assistant</t>
   </si>
   <si>
-    <t>Ahmed Hassan</t>
-  </si>
-  <si>
-    <t>Ahmed Hadary</t>
-  </si>
-  <si>
-    <t>Omar Eid</t>
-  </si>
-  <si>
-    <t>Tarek Fawzi</t>
+    <t>Oscar Karam</t>
+  </si>
+  <si>
+    <t>Dario Quinn</t>
+  </si>
+  <si>
+    <t>Dario Rafiq</t>
+  </si>
+  <si>
+    <t>Zane Mendes</t>
   </si>
   <si>
     <t>Truck Driver</t>
@@ -504,16 +504,16 @@
     <t>Filter Press operator</t>
   </si>
   <si>
-    <t>Ahmed Ali</t>
+    <t>Oscar Hamdan</t>
   </si>
   <si>
     <t>Steel Work Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">E. Mahmoud elsayed </t>
-  </si>
-  <si>
-    <t>Mohamed Sayed</t>
+    <t xml:space="preserve">Eng. Carlos Baig</t>
+  </si>
+  <si>
+    <t>Emil Quinn</t>
   </si>
   <si>
     <t>Chief Storekeeper</t>
@@ -522,34 +522,34 @@
     <t>Technical office</t>
   </si>
   <si>
-    <t>Mostafa Hussein</t>
-  </si>
-  <si>
-    <t>Ismaiil</t>
-  </si>
-  <si>
-    <t>مندوب مشتريات</t>
-  </si>
-  <si>
-    <t>Saiid Zakaria</t>
-  </si>
-  <si>
-    <t>Mohamed Salem</t>
+    <t>Daniel Mendes</t>
+  </si>
+  <si>
+    <t>Cyril Varga</t>
+  </si>
+  <si>
+    <t>Purchasing Officer</t>
+  </si>
+  <si>
+    <t>Hadi Karam</t>
+  </si>
+  <si>
+    <t>Jonas Mendes</t>
   </si>
   <si>
     <t>Storekeeper Assistant</t>
   </si>
   <si>
-    <t>Reda Elsamahi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greater Cairo Metro Line 4 New CP401 Project  - Tunnel 6-12 TBM </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELI PROJECT COORDINATOR / MANAGER </t>
-  </si>
-  <si>
-    <t>Adminstrative &amp; Logistic for Seli Personnel</t>
+    <t>Ivan Darwish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coastal Tunnel Package – Lot 3 – Twin TBM Drives </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPECIALIST PROJECT COORDINATOR / MANAGER </t>
+  </si>
+  <si>
+    <t>Administrative &amp; Logistics for Specialist Personnel</t>
   </si>
   <si>
     <t>Plant Manager - Maintenance &amp; Equip Responsible</t>
@@ -561,10 +561,10 @@
     <t xml:space="preserve"> De.Tunnel Manager</t>
   </si>
   <si>
-    <t>E.Mahmoud Fouad</t>
-  </si>
-  <si>
-    <t>E.Saad Samir</t>
+    <t>Eng. Pavel Darwish</t>
+  </si>
+  <si>
+    <t>Eng. Emil Arslan</t>
   </si>
   <si>
     <t>Workshop Foreman</t>
@@ -573,16 +573,16 @@
     <t>Deputy Plant Manager</t>
   </si>
   <si>
-    <t>E.Hosney</t>
+    <t>Eng. Marco Lind</t>
   </si>
   <si>
     <t>Assistant</t>
   </si>
   <si>
-    <t>E.Mahmoud Salah</t>
-  </si>
-  <si>
-    <t>E.Abdelrahman Mohamed</t>
+    <t>Eng. Aaron Silva</t>
+  </si>
+  <si>
+    <t>Eng. Victor Arslan</t>
   </si>
   <si>
     <t>Electrical Engineer</t>
@@ -591,34 +591,34 @@
     <t>Mechanical Engineer</t>
   </si>
   <si>
-    <t>E.Taher</t>
-  </si>
-  <si>
-    <t>E. Mohamed Elsayed</t>
-  </si>
-  <si>
-    <t>E. Ahmed Elqeey</t>
-  </si>
-  <si>
-    <t>E.Moataz</t>
-  </si>
-  <si>
-    <t>E. Mahmoud Desoky</t>
-  </si>
-  <si>
-    <t>E. Ahmed Khaled</t>
-  </si>
-  <si>
-    <t>إعتماد 2</t>
-  </si>
-  <si>
-    <t>E. Magdy Aboelsoud</t>
+    <t>Eng. Bilal Baig</t>
+  </si>
+  <si>
+    <t>Eng. Leo Quinn</t>
+  </si>
+  <si>
+    <t>Eng. Nabil Karam</t>
+  </si>
+  <si>
+    <t>Eng. Gavin Menon</t>
+  </si>
+  <si>
+    <t>Eng. Ivan Silva</t>
+  </si>
+  <si>
+    <t>Eng. Felix Ortega</t>
+  </si>
+  <si>
+    <t>Approval 2</t>
+  </si>
+  <si>
+    <t>Eng. Umar Silva</t>
   </si>
   <si>
     <t>Discs Repair</t>
   </si>
   <si>
-    <t>إعتماد 3</t>
+    <t>Approval 3</t>
   </si>
   <si>
     <t>Steel Work Manager</t>
@@ -627,10 +627,10 @@
     <t>PLC Electronic Engineer</t>
   </si>
   <si>
-    <t>E. Mohamed Khorshid</t>
-  </si>
-  <si>
-    <t>E. Islam Gomaa</t>
+    <t>Eng. Umar Darwish</t>
+  </si>
+  <si>
+    <t>Eng. Bruno Silva</t>
   </si>
   <si>
     <t xml:space="preserve"> Supervisor</t>
@@ -639,13 +639,13 @@
     <t>TBM Mechanic</t>
   </si>
   <si>
-    <t xml:space="preserve">إعتماد 2 </t>
-  </si>
-  <si>
-    <t>E. Osama Kamal</t>
-  </si>
-  <si>
-    <t>إعتماد 9</t>
+    <t xml:space="preserve">Approval 2 </t>
+  </si>
+  <si>
+    <t>Eng. Samir Hamdan</t>
+  </si>
+  <si>
+    <t>Approval 9</t>
   </si>
   <si>
     <t xml:space="preserve"> Welder</t>
@@ -663,43 +663,43 @@
     <t>TBM Erector (Backup)</t>
   </si>
   <si>
-    <t>Mohamed Hamza</t>
-  </si>
-  <si>
-    <t>Hussen</t>
-  </si>
-  <si>
-    <t>Abdelmenem</t>
-  </si>
-  <si>
-    <t>Fawzy</t>
-  </si>
-  <si>
-    <t>E. Mohamed Samir</t>
+    <t>Hadi Rafiq</t>
+  </si>
+  <si>
+    <t>Oscar Ortega</t>
+  </si>
+  <si>
+    <t>Wael Lind</t>
+  </si>
+  <si>
+    <t>Dario Arslan</t>
+  </si>
+  <si>
+    <t>Eng. Ivan Karam</t>
   </si>
   <si>
     <t>MSV Driver</t>
   </si>
   <si>
-    <t>إعتماد 8</t>
-  </si>
-  <si>
-    <t>E. Mahmoud Refaat</t>
-  </si>
-  <si>
-    <t>E. Mohamed Osama (Line 3)</t>
-  </si>
-  <si>
-    <t>إعتماد 6</t>
+    <t>Approval 8</t>
+  </si>
+  <si>
+    <t>Eng. Emil Costa</t>
+  </si>
+  <si>
+    <t>Eng. Umar Arslan</t>
+  </si>
+  <si>
+    <t>Approval 6</t>
   </si>
   <si>
     <t>WTP Operator (Filter Press)</t>
   </si>
   <si>
-    <t>Ibrahim</t>
-  </si>
-  <si>
-    <t>Mohsen</t>
+    <t>Leo Haddad</t>
+  </si>
+  <si>
+    <t>Felix Faris</t>
   </si>
   <si>
     <t xml:space="preserve">PROJECT SENIOR MANAGER </t>
@@ -708,10 +708,10 @@
     <t>Rack pinion Driver</t>
   </si>
   <si>
-    <t>Mr. Husseyin Tesdimir</t>
-  </si>
-  <si>
-    <t>Mr. Ahmet Bardak</t>
+    <t>Mr. Bilal Varga</t>
+  </si>
+  <si>
+    <t>Mr. Nabil Costa</t>
   </si>
   <si>
     <t>TBM - 1</t>
@@ -837,10 +837,10 @@
     <t>Direct Reporting</t>
   </si>
   <si>
-    <t xml:space="preserve">                                                                                                     SELI OVERSEAS (ROME)</t>
-  </si>
-  <si>
-    <t>Mr. Kamil</t>
+    <t xml:space="preserve">                                                                                                     APEX TUNNEL SERVICES</t>
+  </si>
+  <si>
+    <t>Mr. Samir Rafiq</t>
   </si>
   <si>
     <t xml:space="preserve">                 Plant Team</t>
